--- a/SAM_Opportunities_Report_20260622_PM.xlsx
+++ b/SAM_Opportunities_Report_20260622_PM.xlsx
@@ -14,10 +14,10 @@
     <sheet name="🔧 Specialty Pipeline" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$132</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -849,7 +849,7 @@
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N89"/>
+  <dimension ref="B2:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1330,7 +1330,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>All open Solicitations sorted by urgency  ·  84 records  ·  As of June 22, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
+          <t>All open Solicitations sorted by urgency  ·  87 records  ·  As of June 22, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
         </is>
       </c>
     </row>
@@ -5296,22 +5296,22 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>W9124D26QA266</t>
+          <t>140L2626R0004</t>
         </is>
       </c>
       <c r="D64" s="30" t="inlineStr">
         <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
+          <t>Y--Cauldron Linn Recreation Site Improvements</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>North Chicago, Illinois</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0037</t>
+          <t>140L2626Q0032</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
         <is>
-          <t>Pompeys Pillar Security System Upgrade</t>
+          <t>Indian Springs Vault Toilet</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G65" s="20" t="inlineStr">
@@ -5430,22 +5430,22 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>N6945026R0064</t>
+          <t>W9124D26QA266</t>
         </is>
       </c>
       <c r="D66" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Base Operations Support (BOS) Services at Naval Air Station (NAS) Whiting Field and Outlying Areas</t>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Chicago, Illinois</t>
         </is>
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
-          <t>Jul 14, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="J66" s="17" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="K66" s="41" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000068</t>
+          <t>140L3626Q0037</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
         <is>
-          <t>Beresford Substation Stage 11, South Dakota</t>
+          <t>Pompeys Pillar Security System Upgrade</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G67" s="20" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="J67" s="20" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="K67" s="41" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>N6945026R0064</t>
         </is>
       </c>
       <c r="D68" s="30" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t xml:space="preserve"> Base Operations Support (BOS) Services at Naval Air Station (NAS) Whiting Field and Outlying Areas</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 14, 2026</t>
         </is>
       </c>
       <c r="J68" s="17" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="K68" s="41" t="inlineStr">
@@ -5631,22 +5631,22 @@
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>75F40126R00051</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="D69" s="33" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G69" s="20" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>140P2026R0011</t>
+          <t>140L3626Q0032</t>
         </is>
       </c>
       <c r="D70" s="30" t="inlineStr">
         <is>
-          <t>GLCA Hite</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
@@ -5765,22 +5765,22 @@
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>W9127826RA059</t>
+          <t>75F40126R00051</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>Water Tank Storage</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="G71" s="20" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
         <is>
-          <t>23d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="K71" s="41" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>W912HN26BA008</t>
+          <t>140P2026R0011</t>
         </is>
       </c>
       <c r="D72" s="30" t="inlineStr">
         <is>
-          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
+          <t>GLCA Hite</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>Jul 17, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="J72" s="17" t="inlineStr">
         <is>
-          <t>24d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="K72" s="41" t="inlineStr">
@@ -5892,49 +5892,49 @@
       </c>
     </row>
     <row r="73" ht="32" customHeight="1">
-      <c r="B73" s="36" t="inlineStr">
+      <c r="B73" s="20" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="C73" s="37" t="inlineStr">
-        <is>
-          <t>W50S6T26QA026</t>
-        </is>
-      </c>
-      <c r="D73" s="25" t="inlineStr">
-        <is>
-          <t>Remove Traffic Island and Construct Sloped Concrete Static Display</t>
-        </is>
-      </c>
-      <c r="E73" s="37" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="F73" s="37" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="G73" s="38" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H73" s="37" t="inlineStr">
-        <is>
-          <t>$25K</t>
-        </is>
-      </c>
-      <c r="I73" s="37" t="inlineStr">
-        <is>
-          <t>Jul 17, 2026</t>
-        </is>
-      </c>
-      <c r="J73" s="37" t="inlineStr">
-        <is>
-          <t>24d</t>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>W9127826RA059</t>
+        </is>
+      </c>
+      <c r="D73" s="33" t="inlineStr">
+        <is>
+          <t>Water Tank Storage</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr">
+        <is>
+          <t>Jul 16, 2026</t>
+        </is>
+      </c>
+      <c r="J73" s="20" t="inlineStr">
+        <is>
+          <t>23d</t>
         </is>
       </c>
       <c r="K73" s="41" t="inlineStr">
@@ -5942,17 +5942,17 @@
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L73" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="40" t="inlineStr">
+      <c r="L73" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -5966,127 +5966,127 @@
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>FA301626B0001</t>
+          <t>W912HN26BA008</t>
         </is>
       </c>
       <c r="D74" s="30" t="inlineStr">
         <is>
-          <t>Repair Carswell Ave.</t>
+          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>DWG, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>Jul 17, 2026</t>
+        </is>
+      </c>
+      <c r="J74" s="17" t="inlineStr">
+        <is>
+          <t>24d</t>
+        </is>
+      </c>
+      <c r="K74" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L74" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="B75" s="36" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C75" s="37" t="inlineStr">
+        <is>
+          <t>W50S6T26QA026</t>
+        </is>
+      </c>
+      <c r="D75" s="25" t="inlineStr">
+        <is>
+          <t>Remove Traffic Island and Construct Sloped Concrete Static Display</t>
+        </is>
+      </c>
+      <c r="E75" s="37" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="F75" s="37" t="inlineStr">
+        <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H74" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
+      <c r="G75" s="38" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H75" s="37" t="inlineStr">
+        <is>
+          <t>$25K</t>
+        </is>
+      </c>
+      <c r="I75" s="37" t="inlineStr">
         <is>
           <t>Jul 17, 2026</t>
         </is>
       </c>
-      <c r="J74" s="17" t="inlineStr">
+      <c r="J75" s="37" t="inlineStr">
         <is>
           <t>24d</t>
         </is>
       </c>
-      <c r="K74" s="41" t="inlineStr">
+      <c r="K75" s="41" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L74" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="B75" s="20" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C75" s="20" t="inlineStr">
-        <is>
-          <t>75H70126R00030</t>
-        </is>
-      </c>
-      <c r="D75" s="33" t="inlineStr">
-        <is>
-          <t>Rosebud Lift Station Construction</t>
-        </is>
-      </c>
-      <c r="E75" s="20" t="inlineStr">
-        <is>
-          <t>Rosebud, South Dakota</t>
-        </is>
-      </c>
-      <c r="F75" s="20" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="G75" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H75" s="20" t="inlineStr">
-        <is>
-          <t>$11.8M</t>
-        </is>
-      </c>
-      <c r="I75" s="20" t="inlineStr">
-        <is>
-          <t>Jul 20, 2026</t>
-        </is>
-      </c>
-      <c r="J75" s="20" t="inlineStr">
-        <is>
-          <t>27d</t>
-        </is>
-      </c>
-      <c r="K75" s="41" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L75" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="35" t="inlineStr">
+      <c r="L75" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -6100,17 +6100,17 @@
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>693C73-26-R-000047</t>
+          <t>FA301626B0001</t>
         </is>
       </c>
       <c r="D76" s="30" t="inlineStr">
         <is>
-          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
+          <t>Repair Carswell Ave.</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>DWG, Texas</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>$12.9M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
-          <t>Jul 21, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="J76" s="17" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>24d</t>
         </is>
       </c>
       <c r="K76" s="41" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>W912ES26BA013</t>
+          <t>140P8326Q0046</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
         <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+          <t>LARO-DRILL NEW WATER WELL - SHERMAN HOMES CABINS</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G77" s="20" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>Jul 21, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="J77" s="20" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>24d</t>
         </is>
       </c>
       <c r="K77" s="41" t="inlineStr">
@@ -6227,49 +6227,49 @@
       </c>
     </row>
     <row r="78" ht="32" customHeight="1">
-      <c r="B78" s="36" t="inlineStr">
+      <c r="B78" s="17" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="C78" s="37" t="inlineStr">
-        <is>
-          <t>36C25626R0015</t>
-        </is>
-      </c>
-      <c r="D78" s="25" t="inlineStr">
-        <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
-        </is>
-      </c>
-      <c r="E78" s="37" t="inlineStr">
-        <is>
-          <t>Fayetteville, Arkansas</t>
-        </is>
-      </c>
-      <c r="F78" s="37" t="inlineStr">
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>75H70126R00030</t>
+        </is>
+      </c>
+      <c r="D78" s="30" t="inlineStr">
+        <is>
+          <t>Rosebud Lift Station Construction</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>Rosebud, South Dakota</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="G78" s="38" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H78" s="37" t="inlineStr">
-        <is>
-          <t>$15.0M</t>
-        </is>
-      </c>
-      <c r="I78" s="37" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="J78" s="37" t="inlineStr">
-        <is>
-          <t>30d</t>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>$11.8M</t>
+        </is>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>Jul 20, 2026</t>
+        </is>
+      </c>
+      <c r="J78" s="17" t="inlineStr">
+        <is>
+          <t>27d</t>
         </is>
       </c>
       <c r="K78" s="41" t="inlineStr">
@@ -6277,17 +6277,17 @@
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L78" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="40" t="inlineStr">
+      <c r="L78" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>127EAX26R0006</t>
+          <t>693C73-26-R-000047</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>R3 National Forest’s Roads IDIQ</t>
+          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
         </is>
       </c>
       <c r="E79" s="20" t="inlineStr">
@@ -6326,22 +6326,22 @@
       </c>
       <c r="H79" s="20" t="inlineStr">
         <is>
-          <t>$72.5M</t>
+          <t>$12.9M</t>
         </is>
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 21, 2026</t>
         </is>
       </c>
       <c r="J79" s="20" t="inlineStr">
         <is>
-          <t>31d</t>
-        </is>
-      </c>
-      <c r="K79" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+          <t>28d</t>
+        </is>
+      </c>
+      <c r="K79" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L79" s="20" t="inlineStr">
@@ -6368,127 +6368,127 @@
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>140P6326B0006</t>
+          <t>W912ES26BA013</t>
         </is>
       </c>
       <c r="D80" s="30" t="inlineStr">
         <is>
-          <t>Z--KNRI REPLACE VC SANITARY PLUMBING/SEPTIC</t>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>Stanton, North Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>Jul 21, 2026</t>
+        </is>
+      </c>
+      <c r="J80" s="17" t="inlineStr">
+        <is>
+          <t>28d</t>
+        </is>
+      </c>
+      <c r="K80" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L80" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="B81" s="36" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C81" s="37" t="inlineStr">
+        <is>
+          <t>36C25626R0015</t>
+        </is>
+      </c>
+      <c r="D81" s="25" t="inlineStr">
+        <is>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+        </is>
+      </c>
+      <c r="E81" s="37" t="inlineStr">
+        <is>
+          <t>Fayetteville, Arkansas</t>
+        </is>
+      </c>
+      <c r="F81" s="37" t="inlineStr">
+        <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="G80" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H80" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>Jun 23, 2026</t>
-        </is>
-      </c>
-      <c r="J80" s="17" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K80" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
-        </is>
-      </c>
-      <c r="L80" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="B81" s="20" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="C81" s="20" t="inlineStr">
-        <is>
-          <t>W912P926BA072</t>
-        </is>
-      </c>
-      <c r="D81" s="33" t="inlineStr">
-        <is>
-          <t>Bayou Teche, East and West Calumet Floodgate Approach Channels, Maintenance Dredging, St. Mary Parish, Louisiana ED 26-005</t>
-        </is>
-      </c>
-      <c r="E81" s="20" t="inlineStr">
-        <is>
-          <t>New Orleans, Louisiana</t>
-        </is>
-      </c>
-      <c r="F81" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="G81" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H81" s="20" t="inlineStr">
-        <is>
-          <t>$750K</t>
-        </is>
-      </c>
-      <c r="I81" s="20" t="inlineStr">
-        <is>
-          <t>Jun 23, 2026</t>
-        </is>
-      </c>
-      <c r="J81" s="20" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K81" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
-        </is>
-      </c>
-      <c r="L81" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="35" t="inlineStr">
+      <c r="G81" s="38" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H81" s="37" t="inlineStr">
+        <is>
+          <t>$15.0M</t>
+        </is>
+      </c>
+      <c r="I81" s="37" t="inlineStr">
+        <is>
+          <t>Jul 23, 2026</t>
+        </is>
+      </c>
+      <c r="J81" s="37" t="inlineStr">
+        <is>
+          <t>30d</t>
+        </is>
+      </c>
+      <c r="K81" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L81" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -6502,22 +6502,22 @@
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>140P8426R0002</t>
+          <t>127EAX26R0006</t>
         </is>
       </c>
       <c r="D82" s="30" t="inlineStr">
         <is>
-          <t>Z--Rehab Power and Cooling Systems, Pinnalces NP</t>
+          <t>R3 National Forest’s Roads IDIQ</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>Paicines</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G82" s="17" t="inlineStr">
@@ -6527,22 +6527,22 @@
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$72.5M</t>
         </is>
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="J82" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K82" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>31d</t>
+        </is>
+      </c>
+      <c r="K82" s="42" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="L82" s="17" t="inlineStr">
@@ -6569,22 +6569,22 @@
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>FA441726Q0099</t>
+          <t>140P6326B0006</t>
         </is>
       </c>
       <c r="D83" s="33" t="inlineStr">
         <is>
-          <t>23 STS HPTC Surround Sound Installation</t>
+          <t>Z--KNRI REPLACE VC SANITARY PLUMBING/SEPTIC</t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
         <is>
-          <t>Hurlburt Field, Florida</t>
+          <t>Stanton, North Dakota</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G83" s="20" t="inlineStr">
@@ -6636,22 +6636,22 @@
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>140FC226Q0033</t>
+          <t>W912P926BA072</t>
         </is>
       </c>
       <c r="D84" s="30" t="inlineStr">
         <is>
-          <t>VA-RAPPAHANNOCK RIV NWR-WELL DRILLING</t>
+          <t>Bayou Teche, East and West Calumet Floodgate Approach Channels, Maintenance Dredging, St. Mary Parish, Louisiana ED 26-005</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>New Orleans, Louisiana</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G84" s="17" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$750K</t>
         </is>
       </c>
       <c r="I84" s="17" t="inlineStr">
@@ -6703,17 +6703,17 @@
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
-          <t>140FGA26Q0033</t>
+          <t>140P8426R0002</t>
         </is>
       </c>
       <c r="D85" s="33" t="inlineStr">
         <is>
-          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
+          <t>Z--Rehab Power and Cooling Systems, Pinnalces NP</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Paicines</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>140A1626QD002</t>
+          <t>FA441726Q0099</t>
         </is>
       </c>
       <c r="D86" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AIRR Security Cameras &amp; Badging for BTFA</t>
+          <t>23 STS HPTC Surround Sound Installation</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Hurlburt Field, Florida</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="C87" s="20" t="inlineStr">
         <is>
-          <t>140FS226Q0120</t>
+          <t>140FC226Q0033</t>
         </is>
       </c>
       <c r="D87" s="33" t="inlineStr">
         <is>
-          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
+          <t>VA-RAPPAHANNOCK RIV NWR-WELL DRILLING</t>
         </is>
       </c>
       <c r="E87" s="20" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>140FC126R0025</t>
+          <t>140FGA26Q0033</t>
         </is>
       </c>
       <c r="D88" s="30" t="inlineStr">
         <is>
-          <t>Y--Hasty Point Rice Trunk &amp;</t>
+          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G88" s="17" t="inlineStr">
@@ -6971,67 +6971,268 @@
       </c>
       <c r="C89" s="20" t="inlineStr">
         <is>
+          <t>140A1626QD002</t>
+        </is>
+      </c>
+      <c r="D89" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> AIRR Security Cameras &amp; Badging for BTFA</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="G89" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H89" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="20" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026</t>
+        </is>
+      </c>
+      <c r="J89" s="20" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="K89" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L89" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M89" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1">
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>140FS226Q0120</t>
+        </is>
+      </c>
+      <c r="D90" s="30" t="inlineStr">
+        <is>
+          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026</t>
+        </is>
+      </c>
+      <c r="J90" s="17" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="K90" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L90" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M90" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N90" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C91" s="20" t="inlineStr">
+        <is>
+          <t>140FC126R0025</t>
+        </is>
+      </c>
+      <c r="D91" s="33" t="inlineStr">
+        <is>
+          <t>Y--Hasty Point Rice Trunk &amp;</t>
+        </is>
+      </c>
+      <c r="E91" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F91" s="20" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="G91" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H91" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026</t>
+        </is>
+      </c>
+      <c r="J91" s="20" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="K91" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L91" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M91" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
           <t>W912P8-26-B-A072</t>
         </is>
       </c>
-      <c r="D89" s="33" t="inlineStr">
+      <c r="D92" s="30" t="inlineStr">
         <is>
           <t>Bayou Teche, East and West Calumet Floodgate Approach Channels, Maintenance Dredging, St. Mary Parish, Louisiana ED 26-005</t>
         </is>
       </c>
-      <c r="E89" s="20" t="inlineStr">
+      <c r="E92" s="17" t="inlineStr">
         <is>
           <t>New Orleans, Louisiana</t>
         </is>
       </c>
-      <c r="F89" s="20" t="inlineStr">
+      <c r="F92" s="17" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="G89" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H89" s="20" t="inlineStr">
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H92" s="17" t="inlineStr">
         <is>
           <t>$750K</t>
         </is>
       </c>
-      <c r="I89" s="20" t="inlineStr">
+      <c r="I92" s="17" t="inlineStr">
         <is>
           <t>Jun 23, 2026</t>
         </is>
       </c>
-      <c r="J89" s="20" t="inlineStr">
+      <c r="J92" s="17" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="K89" s="18" t="inlineStr">
+      <c r="K92" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L89" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M89" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N89" s="35" t="inlineStr">
+      <c r="L92" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M92" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N92" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:N89"/>
+  <autoFilter ref="B5:N92"/>
   <mergeCells count="2">
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B2:N2"/>
@@ -7121,6 +7322,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N88" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N90" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N91" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7133,7 +7337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K48"/>
+  <dimension ref="B2:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7161,7 +7365,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>Early-stage opportunities to monitor  ·  43 records  (5 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
+          <t>Early-stage opportunities to monitor  ·  41 records  (5 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
         </is>
       </c>
     </row>
@@ -8625,12 +8829,12 @@
     <row r="33" ht="32" customHeight="1">
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0004</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C33" s="33" t="inlineStr">
         <is>
-          <t>Y--Cauldron Linn Recreation Site Improvements</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -8640,7 +8844,7 @@
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -8655,12 +8859,12 @@
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>Jul 13, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -8677,12 +8881,12 @@
     <row r="34" ht="32" customHeight="1">
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0032</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>Y--Indian Springs Vault Toilet</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
@@ -8707,12 +8911,12 @@
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>Jul 13, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J34" s="17" t="inlineStr">
@@ -8729,12 +8933,12 @@
     <row r="35" ht="32" customHeight="1">
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>W912PM26RA0003</t>
         </is>
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -8744,7 +8948,7 @@
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -8759,12 +8963,12 @@
       </c>
       <c r="H35" s="20" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
@@ -8781,22 +8985,22 @@
     <row r="36" ht="32" customHeight="1">
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
@@ -8811,12 +9015,12 @@
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="J36" s="17" t="inlineStr">
@@ -8833,12 +9037,12 @@
     <row r="37" ht="32" customHeight="1">
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>W912PM26RA0003</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C37" s="33" t="inlineStr">
         <is>
-          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -8848,7 +9052,7 @@
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -8863,12 +9067,12 @@
       </c>
       <c r="H37" s="20" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>31d</t>
         </is>
       </c>
       <c r="J37" s="20" t="inlineStr">
@@ -8885,22 +9089,22 @@
     <row r="38" ht="32" customHeight="1">
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>W912EE26RA015</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
@@ -8915,12 +9119,12 @@
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>31d</t>
         </is>
       </c>
       <c r="J38" s="17" t="inlineStr">
@@ -8937,12 +9141,12 @@
     <row r="39" ht="32" customHeight="1">
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C39" s="33" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -8989,22 +9193,22 @@
     <row r="40" ht="32" customHeight="1">
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>140P6326B0008</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Medora, North Dakota</t>
         </is>
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
@@ -9019,12 +9223,12 @@
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
-          <t>31d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J40" s="17" t="inlineStr">
@@ -9041,12 +9245,12 @@
     <row r="41" ht="32" customHeight="1">
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0017</t>
+          <t>140P8526Q0083</t>
         </is>
       </c>
       <c r="C41" s="33" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -9056,7 +9260,7 @@
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -9071,12 +9275,12 @@
       </c>
       <c r="H41" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I41" s="20" t="inlineStr">
         <is>
-          <t>31d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J41" s="20" t="inlineStr">
@@ -9093,22 +9297,22 @@
     <row r="42" ht="32" customHeight="1">
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>140P6326B0008</t>
+          <t>140P9726Q0046</t>
         </is>
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t>Medora, North Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr">
@@ -9123,12 +9327,12 @@
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J42" s="17" t="inlineStr">
@@ -9145,22 +9349,22 @@
     <row r="43" ht="32" customHeight="1">
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>140P8526Q0083</t>
+          <t>W50S85-26-B-A007</t>
         </is>
       </c>
       <c r="C43" s="33" t="inlineStr">
         <is>
-          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
+          <t>Feeder #7 Repair</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Selfridge ANGB, Michigan</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
@@ -9175,12 +9379,12 @@
       </c>
       <c r="H43" s="20" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J43" s="20" t="inlineStr">
@@ -9197,22 +9401,22 @@
     <row r="44" ht="32" customHeight="1">
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>140P9726Q0046</t>
+          <t>W912DQ26QA063</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stockton, Missouri</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
@@ -9227,12 +9431,12 @@
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J44" s="17" t="inlineStr">
@@ -9249,22 +9453,22 @@
     <row r="45" ht="32" customHeight="1">
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>W50S85-26-B-A007</t>
+          <t>140R4025R0017</t>
         </is>
       </c>
       <c r="C45" s="33" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
@@ -9279,12 +9483,12 @@
       </c>
       <c r="H45" s="20" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>23d</t>
         </is>
       </c>
       <c r="J45" s="20" t="inlineStr">
@@ -9301,22 +9505,22 @@
     <row r="46" ht="32" customHeight="1">
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>W912DQ26QA063</t>
+          <t>W15QKN26RA070</t>
         </is>
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+          <t>W15QKN-26-R-A070 - Sources Sought for Building 602 Motor Pool Full Depth Reclamation and Paving at Fort Devens, MA</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>Stockton, Missouri</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F46" s="17" t="inlineStr">
@@ -9331,12 +9535,12 @@
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J46" s="17" t="inlineStr">
@@ -9350,112 +9554,8 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>140R4025R0017</t>
-        </is>
-      </c>
-      <c r="C47" s="33" t="inlineStr">
-        <is>
-          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E47" s="20" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F47" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G47" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="20" t="inlineStr">
-        <is>
-          <t>Jul 16, 2026</t>
-        </is>
-      </c>
-      <c r="I47" s="20" t="inlineStr">
-        <is>
-          <t>23d</t>
-        </is>
-      </c>
-      <c r="J47" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K47" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>W15QKN26RA070</t>
-        </is>
-      </c>
-      <c r="C48" s="30" t="inlineStr">
-        <is>
-          <t>W15QKN-26-R-A070 - Sources Sought for Building 602 Motor Pool Full Depth Reclamation and Paving at Fort Devens, MA</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E48" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="17" t="inlineStr">
-        <is>
-          <t>Jun 24, 2026</t>
-        </is>
-      </c>
-      <c r="I48" s="17" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="J48" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K48" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="B5:K48"/>
+  <autoFilter ref="B5:K46"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -9471,7 +9571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K132"/>
+  <dimension ref="B2:K133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9499,7 +9599,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>Complete data  ·  127 records  ·  June 22, 2026</t>
+          <t>Complete data  ·  128 records  ·  June 22, 2026</t>
         </is>
       </c>
     </row>
@@ -12575,22 +12675,22 @@
     <row r="64" ht="28" customHeight="1">
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>W9124D26QA266</t>
+          <t>140L2626R0004</t>
         </is>
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>USMEPCOM Low Voltage Cable Removal</t>
+          <t>Y--Cauldron Linn Recreation Site Improvements</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>North Chicago, Illinois</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr">
@@ -12627,12 +12727,12 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>140L3626Q0037</t>
+          <t>140L2626Q0032</t>
         </is>
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
-          <t>Pompeys Pillar Security System Upgrade</t>
+          <t>Indian Springs Vault Toilet</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
@@ -12642,7 +12742,7 @@
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
@@ -12679,22 +12779,22 @@
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>N6945026R0064</t>
+          <t>W9124D26QA266</t>
         </is>
       </c>
       <c r="C66" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Base Operations Support (BOS) Services at Naval Air Station (NAS) Whiting Field and Outlying Areas</t>
+          <t>USMEPCOM Low Voltage Cable Removal</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Chicago, Illinois</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F66" s="17" t="inlineStr">
@@ -12709,12 +12809,12 @@
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>Jul 14, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="J66" s="17" t="inlineStr">
@@ -12731,12 +12831,12 @@
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000068</t>
+          <t>140L3626Q0037</t>
         </is>
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>Beresford Substation Stage 11, South Dakota</t>
+          <t>Pompeys Pillar Security System Upgrade</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -12746,7 +12846,7 @@
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
@@ -12761,12 +12861,12 @@
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 13, 2026</t>
         </is>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="J67" s="20" t="inlineStr">
@@ -12783,12 +12883,12 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>N6945026R0064</t>
         </is>
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t xml:space="preserve"> Base Operations Support (BOS) Services at Naval Air Station (NAS) Whiting Field and Outlying Areas</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -12798,7 +12898,7 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
@@ -12813,12 +12913,12 @@
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 14, 2026</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="J68" s="17" t="inlineStr">
@@ -12835,22 +12935,22 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>75F40126R00051</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
@@ -12887,12 +12987,12 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>140P2026R0011</t>
+          <t>140L3626Q0032</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>GLCA Hite</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
@@ -12902,7 +13002,7 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
@@ -12939,22 +13039,22 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>W9127826RA059</t>
+          <t>75F40126R00051</t>
         </is>
       </c>
       <c r="C71" s="33" t="inlineStr">
         <is>
-          <t>Water Tank Storage</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
@@ -12969,12 +13069,12 @@
       </c>
       <c r="H71" s="20" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>23d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
@@ -12991,12 +13091,12 @@
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>W912HN26BA008</t>
+          <t>140P2026R0011</t>
         </is>
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
+          <t>GLCA Hite</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
@@ -13021,12 +13121,12 @@
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>Jul 17, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>24d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="J72" s="17" t="inlineStr">
@@ -13041,52 +13141,52 @@
       </c>
     </row>
     <row r="73" ht="28" customHeight="1">
-      <c r="B73" s="37" t="inlineStr">
-        <is>
-          <t>W50S6T26QA026</t>
-        </is>
-      </c>
-      <c r="C73" s="25" t="inlineStr">
-        <is>
-          <t>Remove Traffic Island and Construct Sloped Concrete Static Display</t>
-        </is>
-      </c>
-      <c r="D73" s="37" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="E73" s="37" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F73" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G73" s="37" t="inlineStr">
-        <is>
-          <t>$25K</t>
-        </is>
-      </c>
-      <c r="H73" s="37" t="inlineStr">
-        <is>
-          <t>Jul 17, 2026</t>
-        </is>
-      </c>
-      <c r="I73" s="37" t="inlineStr">
-        <is>
-          <t>24d</t>
-        </is>
-      </c>
-      <c r="J73" s="37" t="inlineStr">
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>W9127826RA059</t>
+        </is>
+      </c>
+      <c r="C73" s="33" t="inlineStr">
+        <is>
+          <t>Water Tank Storage</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>Jul 16, 2026</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr">
+        <is>
+          <t>23d</t>
+        </is>
+      </c>
+      <c r="J73" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K73" s="40" t="inlineStr">
+      <c r="K73" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13095,102 +13195,102 @@
     <row r="74" ht="28" customHeight="1">
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>FA301626B0001</t>
+          <t>W912HN26BA008</t>
         </is>
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>Repair Carswell Ave.</t>
+          <t>FY26 Brunswick Inner Harbor Dredging Project</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>DWG, Texas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>Jul 17, 2026</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>24d</t>
+        </is>
+      </c>
+      <c r="J74" s="17" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="B75" s="37" t="inlineStr">
+        <is>
+          <t>W50S6T26QA026</t>
+        </is>
+      </c>
+      <c r="C75" s="25" t="inlineStr">
+        <is>
+          <t>Remove Traffic Island and Construct Sloped Concrete Static Display</t>
+        </is>
+      </c>
+      <c r="D75" s="37" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="E75" s="37" t="inlineStr">
+        <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F74" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="17" t="inlineStr">
+      <c r="F75" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G75" s="37" t="inlineStr">
+        <is>
+          <t>$25K</t>
+        </is>
+      </c>
+      <c r="H75" s="37" t="inlineStr">
         <is>
           <t>Jul 17, 2026</t>
         </is>
       </c>
-      <c r="I74" s="17" t="inlineStr">
+      <c r="I75" s="37" t="inlineStr">
         <is>
           <t>24d</t>
         </is>
       </c>
-      <c r="J74" s="17" t="inlineStr">
+      <c r="J75" s="37" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1">
-      <c r="B75" s="20" t="inlineStr">
-        <is>
-          <t>75H70126R00030</t>
-        </is>
-      </c>
-      <c r="C75" s="33" t="inlineStr">
-        <is>
-          <t>Rosebud Lift Station Construction</t>
-        </is>
-      </c>
-      <c r="D75" s="20" t="inlineStr">
-        <is>
-          <t>Rosebud, South Dakota</t>
-        </is>
-      </c>
-      <c r="E75" s="20" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F75" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G75" s="20" t="inlineStr">
-        <is>
-          <t>$11.8M</t>
-        </is>
-      </c>
-      <c r="H75" s="20" t="inlineStr">
-        <is>
-          <t>Jul 20, 2026</t>
-        </is>
-      </c>
-      <c r="I75" s="20" t="inlineStr">
-        <is>
-          <t>27d</t>
-        </is>
-      </c>
-      <c r="J75" s="20" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K75" s="35" t="inlineStr">
+      <c r="K75" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13199,17 +13299,17 @@
     <row r="76" ht="28" customHeight="1">
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>693C73-26-R-000047</t>
+          <t>FA301626B0001</t>
         </is>
       </c>
       <c r="C76" s="30" t="inlineStr">
         <is>
-          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
+          <t>Repair Carswell Ave.</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>DWG, Texas</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -13224,17 +13324,17 @@
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>$12.9M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>Jul 21, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>24d</t>
         </is>
       </c>
       <c r="J76" s="17" t="inlineStr">
@@ -13251,12 +13351,12 @@
     <row r="77" ht="28" customHeight="1">
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>W912ES26BA013</t>
+          <t>140P8326Q0046</t>
         </is>
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+          <t>LARO-DRILL NEW WATER WELL - SHERMAN HOMES CABINS</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
@@ -13266,7 +13366,7 @@
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
@@ -13281,12 +13381,12 @@
       </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
-          <t>Jul 21, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>28d</t>
+          <t>24d</t>
         </is>
       </c>
       <c r="J77" s="20" t="inlineStr">
@@ -13301,52 +13401,52 @@
       </c>
     </row>
     <row r="78" ht="28" customHeight="1">
-      <c r="B78" s="37" t="inlineStr">
-        <is>
-          <t>36C25626R0015</t>
-        </is>
-      </c>
-      <c r="C78" s="25" t="inlineStr">
-        <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
-        </is>
-      </c>
-      <c r="D78" s="37" t="inlineStr">
-        <is>
-          <t>Fayetteville, Arkansas</t>
-        </is>
-      </c>
-      <c r="E78" s="37" t="inlineStr">
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>75H70126R00030</t>
+        </is>
+      </c>
+      <c r="C78" s="30" t="inlineStr">
+        <is>
+          <t>Rosebud Lift Station Construction</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>Rosebud, South Dakota</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="F78" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G78" s="37" t="inlineStr">
-        <is>
-          <t>$15.0M</t>
-        </is>
-      </c>
-      <c r="H78" s="37" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="I78" s="37" t="inlineStr">
-        <is>
-          <t>30d</t>
-        </is>
-      </c>
-      <c r="J78" s="37" t="inlineStr">
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>$11.8M</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>Jul 20, 2026</t>
+        </is>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>27d</t>
+        </is>
+      </c>
+      <c r="J78" s="17" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K78" s="40" t="inlineStr">
+      <c r="K78" s="32" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13355,12 +13455,12 @@
     <row r="79" ht="28" customHeight="1">
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>127EAX26R0006</t>
+          <t>693C73-26-R-000047</t>
         </is>
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>R3 National Forest’s Roads IDIQ</t>
+          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -13380,17 +13480,17 @@
       </c>
       <c r="G79" s="20" t="inlineStr">
         <is>
-          <t>$72.5M</t>
+          <t>$12.9M</t>
         </is>
       </c>
       <c r="H79" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 21, 2026</t>
         </is>
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>31d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="J79" s="20" t="inlineStr">
@@ -13407,102 +13507,102 @@
     <row r="80" ht="28" customHeight="1">
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>140P6326B0006</t>
+          <t>W912ES26BA013</t>
         </is>
       </c>
       <c r="C80" s="30" t="inlineStr">
         <is>
-          <t>Z--KNRI REPLACE VC SANITARY PLUMBING/SEPTIC</t>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t>Stanton, North Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>Jul 21, 2026</t>
+        </is>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>28d</t>
+        </is>
+      </c>
+      <c r="J80" s="17" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="B81" s="37" t="inlineStr">
+        <is>
+          <t>36C25626R0015</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+        </is>
+      </c>
+      <c r="D81" s="37" t="inlineStr">
+        <is>
+          <t>Fayetteville, Arkansas</t>
+        </is>
+      </c>
+      <c r="E81" s="37" t="inlineStr">
+        <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="F80" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G80" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="17" t="inlineStr">
-        <is>
-          <t>Jun 23, 2026</t>
-        </is>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="J80" s="17" t="inlineStr">
+      <c r="F81" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G81" s="37" t="inlineStr">
+        <is>
+          <t>$15.0M</t>
+        </is>
+      </c>
+      <c r="H81" s="37" t="inlineStr">
+        <is>
+          <t>Jul 23, 2026</t>
+        </is>
+      </c>
+      <c r="I81" s="37" t="inlineStr">
+        <is>
+          <t>30d</t>
+        </is>
+      </c>
+      <c r="J81" s="37" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="B81" s="20" t="inlineStr">
-        <is>
-          <t>W912P926BA072</t>
-        </is>
-      </c>
-      <c r="C81" s="33" t="inlineStr">
-        <is>
-          <t>Bayou Teche, East and West Calumet Floodgate Approach Channels, Maintenance Dredging, St. Mary Parish, Louisiana ED 26-005</t>
-        </is>
-      </c>
-      <c r="D81" s="20" t="inlineStr">
-        <is>
-          <t>New Orleans, Louisiana</t>
-        </is>
-      </c>
-      <c r="E81" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F81" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G81" s="20" t="inlineStr">
-        <is>
-          <t>$750K</t>
-        </is>
-      </c>
-      <c r="H81" s="20" t="inlineStr">
-        <is>
-          <t>Jun 23, 2026</t>
-        </is>
-      </c>
-      <c r="I81" s="20" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="J81" s="20" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K81" s="35" t="inlineStr">
+      <c r="K81" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13511,22 +13611,22 @@
     <row r="82" ht="28" customHeight="1">
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>140P8426R0002</t>
+          <t>127EAX26R0006</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>Z--Rehab Power and Cooling Systems, Pinnalces NP</t>
+          <t>R3 National Forest’s Roads IDIQ</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t>Paicines</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F82" s="17" t="inlineStr">
@@ -13536,17 +13636,17 @@
       </c>
       <c r="G82" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$72.5M</t>
         </is>
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>31d</t>
         </is>
       </c>
       <c r="J82" s="17" t="inlineStr">
@@ -13563,22 +13663,22 @@
     <row r="83" ht="28" customHeight="1">
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>FA441726Q0099</t>
+          <t>140P6326B0006</t>
         </is>
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
-          <t>23 STS HPTC Surround Sound Installation</t>
+          <t>Z--KNRI REPLACE VC SANITARY PLUMBING/SEPTIC</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
         <is>
-          <t>Hurlburt Field, Florida</t>
+          <t>Stanton, North Dakota</t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
@@ -13615,22 +13715,22 @@
     <row r="84" ht="28" customHeight="1">
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>140FC226Q0033</t>
+          <t>W912P926BA072</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>VA-RAPPAHANNOCK RIV NWR-WELL DRILLING</t>
+          <t>Bayou Teche, East and West Calumet Floodgate Approach Channels, Maintenance Dredging, St. Mary Parish, Louisiana ED 26-005</t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>New Orleans, Louisiana</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
@@ -13640,7 +13740,7 @@
       </c>
       <c r="G84" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$750K</t>
         </is>
       </c>
       <c r="H84" s="17" t="inlineStr">
@@ -13667,17 +13767,17 @@
     <row r="85" ht="28" customHeight="1">
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>140FGA26Q0033</t>
+          <t>140P8426R0002</t>
         </is>
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
-          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
+          <t>Z--Rehab Power and Cooling Systems, Pinnalces NP</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Paicines</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
@@ -13719,17 +13819,17 @@
     <row r="86" ht="28" customHeight="1">
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>140A1626QD002</t>
+          <t>FA441726Q0099</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AIRR Security Cameras &amp; Badging for BTFA</t>
+          <t>23 STS HPTC Surround Sound Installation</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Hurlburt Field, Florida</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -13771,12 +13871,12 @@
     <row r="87" ht="28" customHeight="1">
       <c r="B87" s="20" t="inlineStr">
         <is>
-          <t>140FS226Q0120</t>
+          <t>140FC226Q0033</t>
         </is>
       </c>
       <c r="C87" s="33" t="inlineStr">
         <is>
-          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
+          <t>VA-RAPPAHANNOCK RIV NWR-WELL DRILLING</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -13823,12 +13923,12 @@
     <row r="88" ht="28" customHeight="1">
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>140FC126R0025</t>
+          <t>140FGA26Q0033</t>
         </is>
       </c>
       <c r="C88" s="30" t="inlineStr">
         <is>
-          <t>Y--Hasty Point Rice Trunk &amp;</t>
+          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
         </is>
       </c>
       <c r="D88" s="17" t="inlineStr">
@@ -13838,7 +13938,7 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F88" s="17" t="inlineStr">
@@ -13875,22 +13975,22 @@
     <row r="89" ht="28" customHeight="1">
       <c r="B89" s="20" t="inlineStr">
         <is>
-          <t>W912P8-26-B-A072</t>
+          <t>140A1626QD002</t>
         </is>
       </c>
       <c r="C89" s="33" t="inlineStr">
         <is>
-          <t>Bayou Teche, East and West Calumet Floodgate Approach Channels, Maintenance Dredging, St. Mary Parish, Louisiana ED 26-005</t>
+          <t xml:space="preserve"> AIRR Security Cameras &amp; Badging for BTFA</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
         <is>
-          <t>New Orleans, Louisiana</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E89" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
@@ -13900,7 +14000,7 @@
       </c>
       <c r="G89" s="20" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H89" s="20" t="inlineStr">
@@ -13927,102 +14027,102 @@
     <row r="90" ht="28" customHeight="1">
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>GROUP1-24-R-W001</t>
+          <t>140FS226Q0120</t>
         </is>
       </c>
       <c r="C90" s="30" t="inlineStr">
         <is>
-          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
+          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
         </is>
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026</t>
+        </is>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="J90" s="17" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K90" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>140FC126R0025</t>
+        </is>
+      </c>
+      <c r="C91" s="33" t="inlineStr">
+        <is>
+          <t>Y--Hasty Point Rice Trunk &amp;</t>
+        </is>
+      </c>
+      <c r="D91" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E91" s="20" t="inlineStr">
+        <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="F90" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G90" s="17" t="inlineStr">
-        <is>
-          <t>$17.5M</t>
-        </is>
-      </c>
-      <c r="H90" s="17" t="inlineStr">
-        <is>
-          <t>Jun 24, 2026</t>
-        </is>
-      </c>
-      <c r="I90" s="17" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="J90" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K90" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="28" customHeight="1">
-      <c r="B91" s="37" t="inlineStr">
-        <is>
-          <t>36C26126R0050</t>
-        </is>
-      </c>
-      <c r="C91" s="25" t="inlineStr">
-        <is>
-          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
-        </is>
-      </c>
-      <c r="D91" s="37" t="inlineStr">
-        <is>
-          <t>Reno, NV</t>
-        </is>
-      </c>
-      <c r="E91" s="37" t="inlineStr">
-        <is>
-          <t>238210</t>
-        </is>
-      </c>
-      <c r="F91" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G91" s="37" t="inlineStr">
-        <is>
-          <t>$5.0M</t>
-        </is>
-      </c>
-      <c r="H91" s="37" t="inlineStr">
-        <is>
-          <t>Jun 24, 2026</t>
-        </is>
-      </c>
-      <c r="I91" s="37" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="J91" s="37" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K91" s="40" t="inlineStr">
+      <c r="F91" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G91" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="20" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026</t>
+        </is>
+      </c>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="J91" s="20" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K91" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14031,22 +14131,22 @@
     <row r="92" ht="28" customHeight="1">
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>W15QKN26RA070</t>
+          <t>W912P8-26-B-A072</t>
         </is>
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
-          <t>W15QKN-26-R-A070 - Sources Sought for Building 602 Motor Pool Full Depth Reclamation and Paving at Fort Devens, MA</t>
+          <t>Bayou Teche, East and West Calumet Floodgate Approach Channels, Maintenance Dredging, St. Mary Parish, Louisiana ED 26-005</t>
         </is>
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>New Orleans, Louisiana</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -14056,22 +14156,22 @@
       </c>
       <c r="G92" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$750K</t>
         </is>
       </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J92" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K92" s="32" t="inlineStr">
@@ -14083,22 +14183,22 @@
     <row r="93" ht="28" customHeight="1">
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>140P8526Q0083</t>
+          <t>GROUP1-24-R-W001</t>
         </is>
       </c>
       <c r="C93" s="33" t="inlineStr">
         <is>
-          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
+          <t>Atlantic Intracoastal Waterway Maintenance Dredging</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="E93" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -14108,17 +14208,17 @@
       </c>
       <c r="G93" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$17.5M</t>
         </is>
       </c>
       <c r="H93" s="20" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="I93" s="20" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J93" s="20" t="inlineStr">
@@ -14133,52 +14233,52 @@
       </c>
     </row>
     <row r="94" ht="28" customHeight="1">
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>140P9726Q0046</t>
-        </is>
-      </c>
-      <c r="C94" s="30" t="inlineStr">
-        <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
-        </is>
-      </c>
-      <c r="D94" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E94" s="17" t="inlineStr">
+      <c r="B94" s="37" t="inlineStr">
+        <is>
+          <t>36C26126R0050</t>
+        </is>
+      </c>
+      <c r="C94" s="25" t="inlineStr">
+        <is>
+          <t>6150--FY26 NRM 654-26-020 | 654-26-2-6059-0042 | Bldg 12 Pump  Power Relocation | VA Sierra Nevada Health Care System  Reno, NV</t>
+        </is>
+      </c>
+      <c r="D94" s="37" t="inlineStr">
+        <is>
+          <t>Reno, NV</t>
+        </is>
+      </c>
+      <c r="E94" s="37" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F94" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G94" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H94" s="17" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="I94" s="17" t="inlineStr">
-        <is>
-          <t>2d</t>
-        </is>
-      </c>
-      <c r="J94" s="17" t="inlineStr">
+      <c r="F94" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G94" s="37" t="inlineStr">
+        <is>
+          <t>$5.0M</t>
+        </is>
+      </c>
+      <c r="H94" s="37" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026</t>
+        </is>
+      </c>
+      <c r="I94" s="37" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="J94" s="37" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K94" s="32" t="inlineStr">
+      <c r="K94" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14187,22 +14287,22 @@
     <row r="95" ht="28" customHeight="1">
       <c r="B95" s="20" t="inlineStr">
         <is>
-          <t>W50S85-26-B-A007</t>
+          <t>W15QKN26RA070</t>
         </is>
       </c>
       <c r="C95" s="33" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>W15QKN-26-R-A070 - Sources Sought for Building 602 Motor Pool Full Depth Reclamation and Paving at Fort Devens, MA</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
@@ -14217,12 +14317,12 @@
       </c>
       <c r="H95" s="20" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="I95" s="20" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J95" s="20" t="inlineStr">
@@ -14239,12 +14339,12 @@
     <row r="96" ht="28" customHeight="1">
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>W912DR26BA007</t>
+          <t>140P8526Q0083</t>
         </is>
       </c>
       <c r="C96" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
+          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
         </is>
       </c>
       <c r="D96" s="17" t="inlineStr">
@@ -14254,7 +14354,7 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F96" s="17" t="inlineStr">
@@ -14264,17 +14364,17 @@
       </c>
       <c r="G96" s="17" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H96" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="J96" s="17" t="inlineStr">
@@ -14289,52 +14389,52 @@
       </c>
     </row>
     <row r="97" ht="28" customHeight="1">
-      <c r="B97" s="37" t="inlineStr">
-        <is>
-          <t>36C24726Q0610</t>
-        </is>
-      </c>
-      <c r="C97" s="25" t="inlineStr">
-        <is>
-          <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
-        </is>
-      </c>
-      <c r="D97" s="37" t="inlineStr">
-        <is>
-          <t>Columbia, South Carolina</t>
-        </is>
-      </c>
-      <c r="E97" s="37" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F97" s="37" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G97" s="37" t="inlineStr">
-        <is>
-          <t>$47.0M</t>
-        </is>
-      </c>
-      <c r="H97" s="37" t="inlineStr">
-        <is>
-          <t>Jul 01, 2026</t>
-        </is>
-      </c>
-      <c r="I97" s="37" t="inlineStr">
-        <is>
-          <t>8d</t>
-        </is>
-      </c>
-      <c r="J97" s="37" t="inlineStr">
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>140P9726Q0046</t>
+        </is>
+      </c>
+      <c r="C97" s="33" t="inlineStr">
+        <is>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+        </is>
+      </c>
+      <c r="D97" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F97" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G97" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="20" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026</t>
+        </is>
+      </c>
+      <c r="I97" s="20" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="J97" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K97" s="40" t="inlineStr">
+      <c r="K97" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14343,22 +14443,22 @@
     <row r="98" ht="28" customHeight="1">
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
+          <t>W50S85-26-B-A007</t>
         </is>
       </c>
       <c r="C98" s="30" t="inlineStr">
         <is>
-          <t>Repair Hush House Concrete B3857</t>
+          <t>Feeder #7 Repair</t>
         </is>
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Selfridge ANGB, Michigan</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
@@ -14368,17 +14468,17 @@
       </c>
       <c r="G98" s="17" t="inlineStr">
         <is>
-          <t>$23.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H98" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J98" s="17" t="inlineStr">
@@ -14395,12 +14495,12 @@
     <row r="99" ht="28" customHeight="1">
       <c r="B99" s="20" t="inlineStr">
         <is>
-          <t>W9133L26BA010</t>
+          <t>W912DR26BA007</t>
         </is>
       </c>
       <c r="C99" s="33" t="inlineStr">
         <is>
-          <t>Air National Guard (ANG) Smart Meters</t>
+          <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -14410,7 +14510,7 @@
       </c>
       <c r="E99" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
@@ -14420,17 +14520,17 @@
       </c>
       <c r="G99" s="20" t="inlineStr">
         <is>
-          <t>$4.2M</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H99" s="20" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I99" s="20" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J99" s="20" t="inlineStr">
@@ -14447,22 +14547,22 @@
     <row r="100" ht="28" customHeight="1">
       <c r="B100" s="37" t="inlineStr">
         <is>
-          <t>36C24626R0067</t>
+          <t>36C24726Q0610</t>
         </is>
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
+          <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
         </is>
       </c>
       <c r="D100" s="37" t="inlineStr">
         <is>
-          <t>Hampton, Virginia</t>
+          <t>Columbia, South Carolina</t>
         </is>
       </c>
       <c r="E100" s="37" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F100" s="37" t="inlineStr">
@@ -14472,17 +14572,17 @@
       </c>
       <c r="G100" s="37" t="inlineStr">
         <is>
-          <t>$7.0M</t>
+          <t>$47.0M</t>
         </is>
       </c>
       <c r="H100" s="37" t="inlineStr">
         <is>
-          <t>Jul 13, 2026</t>
+          <t>Jul 01, 2026</t>
         </is>
       </c>
       <c r="I100" s="37" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="J100" s="37" t="inlineStr">
@@ -14499,12 +14599,12 @@
     <row r="101" ht="28" customHeight="1">
       <c r="B101" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0004</t>
+          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
         </is>
       </c>
       <c r="C101" s="33" t="inlineStr">
         <is>
-          <t>Y--Cauldron Linn Recreation Site Improvements</t>
+          <t>Repair Hush House Concrete B3857</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -14514,7 +14614,7 @@
       </c>
       <c r="E101" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
@@ -14524,17 +14624,17 @@
       </c>
       <c r="G101" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="H101" s="20" t="inlineStr">
         <is>
-          <t>Jul 13, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I101" s="20" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="J101" s="20" t="inlineStr">
@@ -14551,12 +14651,12 @@
     <row r="102" ht="28" customHeight="1">
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0032</t>
+          <t>W9133L26BA010</t>
         </is>
       </c>
       <c r="C102" s="30" t="inlineStr">
         <is>
-          <t>Y--Indian Springs Vault Toilet</t>
+          <t>Air National Guard (ANG) Smart Meters</t>
         </is>
       </c>
       <c r="D102" s="17" t="inlineStr">
@@ -14566,7 +14666,7 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F102" s="17" t="inlineStr">
@@ -14576,77 +14676,77 @@
       </c>
       <c r="G102" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$4.2M</t>
         </is>
       </c>
       <c r="H102" s="17" t="inlineStr">
         <is>
+          <t>Jul 02, 2026</t>
+        </is>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>9d</t>
+        </is>
+      </c>
+      <c r="J102" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K102" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="28" customHeight="1">
+      <c r="B103" s="37" t="inlineStr">
+        <is>
+          <t>36C24626R0067</t>
+        </is>
+      </c>
+      <c r="C103" s="25" t="inlineStr">
+        <is>
+          <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
+        </is>
+      </c>
+      <c r="D103" s="37" t="inlineStr">
+        <is>
+          <t>Hampton, Virginia</t>
+        </is>
+      </c>
+      <c r="E103" s="37" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F103" s="37" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G103" s="37" t="inlineStr">
+        <is>
+          <t>$7.0M</t>
+        </is>
+      </c>
+      <c r="H103" s="37" t="inlineStr">
+        <is>
           <t>Jul 13, 2026</t>
         </is>
       </c>
-      <c r="I102" s="17" t="inlineStr">
+      <c r="I103" s="37" t="inlineStr">
         <is>
           <t>20d</t>
         </is>
       </c>
-      <c r="J102" s="17" t="inlineStr">
+      <c r="J103" s="37" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K102" s="32" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="B103" s="20" t="inlineStr">
-        <is>
-          <t>W912EE26RA015</t>
-        </is>
-      </c>
-      <c r="C103" s="33" t="inlineStr">
-        <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
-        </is>
-      </c>
-      <c r="D103" s="20" t="inlineStr">
-        <is>
-          <t>Royal, Arkansas</t>
-        </is>
-      </c>
-      <c r="E103" s="20" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F103" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G103" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H103" s="20" t="inlineStr">
-        <is>
-          <t>Jul 15, 2026</t>
-        </is>
-      </c>
-      <c r="I103" s="20" t="inlineStr">
-        <is>
-          <t>22d</t>
-        </is>
-      </c>
-      <c r="J103" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K103" s="35" t="inlineStr">
+      <c r="K103" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14655,22 +14755,22 @@
     <row r="104" ht="28" customHeight="1">
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>140R4025R0017</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C104" s="30" t="inlineStr">
         <is>
-          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F104" s="17" t="inlineStr">
@@ -14685,12 +14785,12 @@
       </c>
       <c r="H104" s="17" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
-          <t>23d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="J104" s="17" t="inlineStr">
@@ -14707,12 +14807,12 @@
     <row r="105" ht="28" customHeight="1">
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>140R4025R0017</t>
         </is>
       </c>
       <c r="C105" s="33" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -14722,7 +14822,7 @@
       </c>
       <c r="E105" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -14737,12 +14837,12 @@
       </c>
       <c r="H105" s="20" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="I105" s="20" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>23d</t>
         </is>
       </c>
       <c r="J105" s="20" t="inlineStr">
@@ -14759,12 +14859,12 @@
     <row r="106" ht="28" customHeight="1">
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C106" s="30" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D106" s="17" t="inlineStr">
@@ -14774,7 +14874,7 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
@@ -14811,12 +14911,12 @@
     <row r="107" ht="28" customHeight="1">
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C107" s="33" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
@@ -14826,7 +14926,7 @@
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
@@ -14841,12 +14941,12 @@
       </c>
       <c r="H107" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I107" s="20" t="inlineStr">
         <is>
-          <t>31d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J107" s="20" t="inlineStr">
@@ -14863,12 +14963,12 @@
     <row r="108" ht="28" customHeight="1">
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C108" s="30" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D108" s="17" t="inlineStr">
@@ -14878,7 +14978,7 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F108" s="17" t="inlineStr">
@@ -14915,12 +15015,12 @@
     <row r="109" ht="28" customHeight="1">
       <c r="B109" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0017</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C109" s="33" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -14930,7 +15030,7 @@
       </c>
       <c r="E109" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -14967,12 +15067,12 @@
     <row r="110" ht="28" customHeight="1">
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0024</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C110" s="30" t="inlineStr">
         <is>
-          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D110" s="17" t="inlineStr">
@@ -14982,7 +15082,7 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F110" s="17" t="inlineStr">
@@ -14992,17 +15092,17 @@
       </c>
       <c r="G110" s="17" t="inlineStr">
         <is>
-          <t>$11.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H110" s="17" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
-          <t>34d</t>
+          <t>31d</t>
         </is>
       </c>
       <c r="J110" s="17" t="inlineStr">
@@ -15019,22 +15119,22 @@
     <row r="111" ht="28" customHeight="1">
       <c r="B111" s="20" t="inlineStr">
         <is>
-          <t>75H70126R00029</t>
+          <t>140FGA26R0024</t>
         </is>
       </c>
       <c r="C111" s="33" t="inlineStr">
         <is>
-          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
+          <t>Y--Sherburne NWR South Loop Autotour Rehab</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
         <is>
-          <t>Pine Ridge, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
@@ -15044,17 +15144,17 @@
       </c>
       <c r="G111" s="20" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>$11.5M</t>
         </is>
       </c>
       <c r="H111" s="20" t="inlineStr">
         <is>
-          <t>Jul 31, 2026</t>
+          <t>Jul 27, 2026</t>
         </is>
       </c>
       <c r="I111" s="20" t="inlineStr">
         <is>
-          <t>38d</t>
+          <t>34d</t>
         </is>
       </c>
       <c r="J111" s="20" t="inlineStr">
@@ -15071,22 +15171,22 @@
     <row r="112" ht="28" customHeight="1">
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0023</t>
+          <t>75H70126R00029</t>
         </is>
       </c>
       <c r="C112" s="30" t="inlineStr">
         <is>
-          <t>Y--Boat Ramp Replacement Project at Kirwin NWR</t>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
         </is>
       </c>
       <c r="D112" s="17" t="inlineStr">
         <is>
-          <t>Kirwin, Kansas</t>
+          <t>Pine Ridge, South Dakota</t>
         </is>
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F112" s="17" t="inlineStr">
@@ -15096,7 +15196,7 @@
       </c>
       <c r="G112" s="17" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H112" s="17" t="inlineStr">
@@ -15123,22 +15223,22 @@
     <row r="113" ht="28" customHeight="1">
       <c r="B113" s="20" t="inlineStr">
         <is>
-          <t>693C73-26-B-000017</t>
+          <t>140FGA26R0023</t>
         </is>
       </c>
       <c r="C113" s="33" t="inlineStr">
         <is>
-          <t>Project VI NP VIIS 100(3) - Rehabilitation of Lameshur Road  in St. John, U.S. Virgin Islands</t>
+          <t>Y--Boat Ramp Replacement Project at Kirwin NWR</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Kirwin, Kansas</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -15148,17 +15248,17 @@
       </c>
       <c r="G113" s="20" t="inlineStr">
         <is>
-          <t>$2.5M</t>
+          <t>$750K</t>
         </is>
       </c>
       <c r="H113" s="20" t="inlineStr">
         <is>
-          <t>Aug 04, 2026</t>
+          <t>Jul 31, 2026</t>
         </is>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>42d</t>
+          <t>38d</t>
         </is>
       </c>
       <c r="J113" s="20" t="inlineStr">
@@ -15175,12 +15275,12 @@
     <row r="114" ht="28" customHeight="1">
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>140L3726R0006</t>
+          <t>693C73-26-B-000017</t>
         </is>
       </c>
       <c r="C114" s="30" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Project VI NP VIIS 100(3) - Rehabilitation of Lameshur Road  in St. John, U.S. Virgin Islands</t>
         </is>
       </c>
       <c r="D114" s="17" t="inlineStr">
@@ -15190,7 +15290,7 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F114" s="17" t="inlineStr">
@@ -15200,17 +15300,17 @@
       </c>
       <c r="G114" s="17" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>$2.5M</t>
         </is>
       </c>
       <c r="H114" s="17" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 04, 2026</t>
         </is>
       </c>
       <c r="I114" s="17" t="inlineStr">
         <is>
-          <t>66d</t>
+          <t>42d</t>
         </is>
       </c>
       <c r="J114" s="17" t="inlineStr">
@@ -15227,12 +15327,12 @@
     <row r="115" ht="28" customHeight="1">
       <c r="B115" s="20" t="inlineStr">
         <is>
-          <t>W912PM26RA0003</t>
+          <t>140L3726R0006</t>
         </is>
       </c>
       <c r="C115" s="33" t="inlineStr">
         <is>
-          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
@@ -15242,7 +15342,7 @@
       </c>
       <c r="E115" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -15252,17 +15352,17 @@
       </c>
       <c r="G115" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="H115" s="20" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>66d</t>
         </is>
       </c>
       <c r="J115" s="20" t="inlineStr">
@@ -15279,12 +15379,12 @@
     <row r="116" ht="28" customHeight="1">
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>W50S7X-26-B-A003</t>
+          <t>W912PM26RA0003</t>
         </is>
       </c>
       <c r="C116" s="30" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>FY26 MOTSU Berms Pre -Solicitation Notice</t>
         </is>
       </c>
       <c r="D116" s="17" t="inlineStr">
@@ -15294,7 +15394,7 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F116" s="17" t="inlineStr">
@@ -15304,7 +15404,7 @@
       </c>
       <c r="G116" s="17" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H116" s="17" t="inlineStr">
@@ -15331,154 +15431,154 @@
     <row r="117" ht="28" customHeight="1">
       <c r="B117" s="20" t="inlineStr">
         <is>
+          <t>W50S7X-26-B-A003</t>
+        </is>
+      </c>
+      <c r="C117" s="33" t="inlineStr">
+        <is>
+          <t>B16 PLC Replacement</t>
+        </is>
+      </c>
+      <c r="D117" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E117" s="20" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F117" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G117" s="20" t="inlineStr">
+        <is>
+          <t>$5.1M</t>
+        </is>
+      </c>
+      <c r="H117" s="20" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026</t>
+        </is>
+      </c>
+      <c r="I117" s="20" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="J117" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K117" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="B118" s="17" t="inlineStr">
+        <is>
           <t>140P5326R0019</t>
         </is>
       </c>
-      <c r="C117" s="33" t="inlineStr">
+      <c r="C118" s="30" t="inlineStr">
         <is>
           <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
-      <c r="D117" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E117" s="20" t="inlineStr">
+      <c r="D118" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E118" s="17" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="F117" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G117" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H117" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I117" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J117" s="20" t="inlineStr">
+      <c r="F118" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G118" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H118" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I118" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J118" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K117" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="28" customHeight="1">
-      <c r="B118" s="37" t="inlineStr">
+      <c r="K118" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="28" customHeight="1">
+      <c r="B119" s="37" t="inlineStr">
         <is>
           <t>36C25726B0007</t>
         </is>
       </c>
-      <c r="C118" s="25" t="inlineStr">
+      <c r="C119" s="25" t="inlineStr">
         <is>
           <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
         </is>
       </c>
-      <c r="D118" s="37" t="inlineStr">
+      <c r="D119" s="37" t="inlineStr">
         <is>
           <t>Waco, Texas</t>
         </is>
       </c>
-      <c r="E118" s="37" t="inlineStr">
+      <c r="E119" s="37" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F118" s="37" t="inlineStr">
+      <c r="F119" s="37" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G118" s="37" t="inlineStr">
+      <c r="G119" s="37" t="inlineStr">
         <is>
           <t>$2.5B</t>
         </is>
       </c>
-      <c r="H118" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I118" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J118" s="37" t="inlineStr">
+      <c r="H119" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I119" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J119" s="37" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K118" s="40" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="28" customHeight="1">
-      <c r="B119" s="20" t="inlineStr">
-        <is>
-          <t>W912HY26BA030</t>
-        </is>
-      </c>
-      <c r="C119" s="33" t="inlineStr">
-        <is>
-          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
-        </is>
-      </c>
-      <c r="D119" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E119" s="20" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F119" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G119" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H119" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I119" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J119" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K119" s="35" t="inlineStr">
+      <c r="K119" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15487,17 +15587,17 @@
     <row r="120" ht="28" customHeight="1">
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>W911WN26BA008</t>
+          <t>W912HY26BA030</t>
         </is>
       </c>
       <c r="C120" s="30" t="inlineStr">
         <is>
-          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
+          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
         </is>
       </c>
       <c r="D120" s="17" t="inlineStr">
         <is>
-          <t>Saltsburg, Pennsylvania</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E120" s="17" t="inlineStr">
@@ -15512,7 +15612,7 @@
       </c>
       <c r="G120" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H120" s="17" t="inlineStr">
@@ -15539,17 +15639,17 @@
     <row r="121" ht="28" customHeight="1">
       <c r="B121" s="20" t="inlineStr">
         <is>
-          <t>PANNWD26P0000028054</t>
+          <t>W911WN26BA008</t>
         </is>
       </c>
       <c r="C121" s="33" t="inlineStr">
         <is>
-          <t>Levee Repair at MRLS L246</t>
+          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Saltsburg, Pennsylvania</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -15564,7 +15664,7 @@
       </c>
       <c r="G121" s="20" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H121" s="20" t="inlineStr">
@@ -15591,12 +15691,12 @@
     <row r="122" ht="28" customHeight="1">
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>140FGA26R0028</t>
+          <t>PANNWD26P0000028054</t>
         </is>
       </c>
       <c r="C122" s="30" t="inlineStr">
         <is>
-          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+          <t>Levee Repair at MRLS L246</t>
         </is>
       </c>
       <c r="D122" s="17" t="inlineStr">
@@ -15606,7 +15706,7 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F122" s="17" t="inlineStr">
@@ -15616,7 +15716,7 @@
       </c>
       <c r="G122" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H122" s="17" t="inlineStr">
@@ -15643,154 +15743,154 @@
     <row r="123" ht="28" customHeight="1">
       <c r="B123" s="20" t="inlineStr">
         <is>
+          <t>140FGA26R0028</t>
+        </is>
+      </c>
+      <c r="C123" s="33" t="inlineStr">
+        <is>
+          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+        </is>
+      </c>
+      <c r="D123" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E123" s="20" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F123" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G123" s="20" t="inlineStr">
+        <is>
+          <t>$11.8M</t>
+        </is>
+      </c>
+      <c r="H123" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I123" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J123" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K123" s="35" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="B124" s="17" t="inlineStr">
+        <is>
           <t>W9128F26RA107</t>
         </is>
       </c>
-      <c r="C123" s="33" t="inlineStr">
+      <c r="C124" s="30" t="inlineStr">
         <is>
           <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
         </is>
       </c>
-      <c r="D123" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E123" s="20" t="inlineStr">
+      <c r="D124" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F123" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G123" s="20" t="inlineStr">
+      <c r="F124" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G124" s="17" t="inlineStr">
         <is>
           <t>$30.0M</t>
         </is>
       </c>
-      <c r="H123" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I123" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J123" s="20" t="inlineStr">
+      <c r="H124" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J124" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K123" s="35" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="B124" s="37" t="inlineStr">
+      <c r="K124" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="B125" s="37" t="inlineStr">
         <is>
           <t>36C24226B0057</t>
         </is>
       </c>
-      <c r="C124" s="25" t="inlineStr">
+      <c r="C125" s="25" t="inlineStr">
         <is>
           <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
         </is>
       </c>
-      <c r="D124" s="37" t="inlineStr">
+      <c r="D125" s="37" t="inlineStr">
         <is>
           <t>Buffalo, New York</t>
         </is>
       </c>
-      <c r="E124" s="37" t="inlineStr">
+      <c r="E125" s="37" t="inlineStr">
         <is>
           <t>237120</t>
         </is>
       </c>
-      <c r="F124" s="37" t="inlineStr">
+      <c r="F125" s="37" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G124" s="37" t="inlineStr">
+      <c r="G125" s="37" t="inlineStr">
         <is>
           <t>$16.2M</t>
         </is>
       </c>
-      <c r="H124" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I124" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J124" s="37" t="inlineStr">
+      <c r="H125" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J125" s="37" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K124" s="40" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="28" customHeight="1">
-      <c r="B125" s="20" t="inlineStr">
-        <is>
-          <t>140P6326B0008</t>
-        </is>
-      </c>
-      <c r="C125" s="33" t="inlineStr">
-        <is>
-          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
-        </is>
-      </c>
-      <c r="D125" s="20" t="inlineStr">
-        <is>
-          <t>Medora, North Dakota</t>
-        </is>
-      </c>
-      <c r="E125" s="20" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F125" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G125" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H125" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I125" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J125" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K125" s="35" t="inlineStr">
+      <c r="K125" s="40" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15799,22 +15899,22 @@
     <row r="126" ht="28" customHeight="1">
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>W912DQ26QA063</t>
+          <t>140P6326B0008</t>
         </is>
       </c>
       <c r="C126" s="30" t="inlineStr">
         <is>
-          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
         </is>
       </c>
       <c r="D126" s="17" t="inlineStr">
         <is>
-          <t>Stockton, Missouri</t>
+          <t>Medora, North Dakota</t>
         </is>
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
@@ -15851,22 +15951,22 @@
     <row r="127" ht="28" customHeight="1">
       <c r="B127" s="20" t="inlineStr">
         <is>
-          <t>W912WJ26QA124</t>
+          <t>W912DQ26QA063</t>
         </is>
       </c>
       <c r="C127" s="33" t="inlineStr">
         <is>
-          <t>Road Gate Painting, Road Gate Installation, Removal and Replacement of Guardrails, Buffumville Lake, Charlton, MA</t>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stockton, Missouri</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -15876,7 +15976,7 @@
       </c>
       <c r="G127" s="20" t="inlineStr">
         <is>
-          <t>$175K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H127" s="20" t="inlineStr">
@@ -15903,22 +16003,22 @@
     <row r="128" ht="28" customHeight="1">
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>W9123826RA018</t>
+          <t>W912WJ26QA124</t>
         </is>
       </c>
       <c r="C128" s="30" t="inlineStr">
         <is>
-          <t>USACE SPK DB Construction – DDJC Centralized Gas and Electric Metering - Tracy, CA</t>
+          <t>Road Gate Painting, Road Gate Installation, Removal and Replacement of Guardrails, Buffumville Lake, Charlton, MA</t>
         </is>
       </c>
       <c r="D128" s="17" t="inlineStr">
         <is>
-          <t>Tracy, California</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
@@ -15928,7 +16028,7 @@
       </c>
       <c r="G128" s="17" t="inlineStr">
         <is>
-          <t>$7.5M</t>
+          <t>$175K</t>
         </is>
       </c>
       <c r="H128" s="17" t="inlineStr">
@@ -15955,22 +16055,22 @@
     <row r="129" ht="28" customHeight="1">
       <c r="B129" s="20" t="inlineStr">
         <is>
-          <t>12445526Q0069</t>
+          <t>W9123826RA018</t>
         </is>
       </c>
       <c r="C129" s="33" t="inlineStr">
         <is>
-          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
+          <t>USACE SPK DB Construction – DDJC Centralized Gas and Electric Metering - Tracy, CA</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tracy, California</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
@@ -15980,22 +16080,22 @@
       </c>
       <c r="G129" s="20" t="inlineStr">
         <is>
-          <t>$25K</t>
+          <t>$7.5M</t>
         </is>
       </c>
       <c r="H129" s="20" t="inlineStr">
         <is>
-          <t>Jun 24, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I129" s="20" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J129" s="20" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K129" s="35" t="inlineStr">
@@ -16007,12 +16107,12 @@
     <row r="130" ht="28" customHeight="1">
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>SP470525R002026</t>
+          <t>12445526Q0069</t>
         </is>
       </c>
       <c r="C130" s="30" t="inlineStr">
         <is>
-          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+          <t>Superior NF ERFO Repairs on FR199 &amp; FR200</t>
         </is>
       </c>
       <c r="D130" s="17" t="inlineStr">
@@ -16022,7 +16122,7 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
@@ -16032,17 +16132,17 @@
       </c>
       <c r="G130" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$25K</t>
         </is>
       </c>
       <c r="H130" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 24, 2026</t>
         </is>
       </c>
       <c r="I130" s="17" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="J130" s="17" t="inlineStr">
@@ -16059,22 +16159,22 @@
     <row r="131" ht="28" customHeight="1">
       <c r="B131" s="20" t="inlineStr">
         <is>
-          <t>140R6026R0016</t>
+          <t>SP470525R002026</t>
         </is>
       </c>
       <c r="C131" s="33" t="inlineStr">
         <is>
-          <t>Z--Webster Dam, Spillway Radial Gates Repair, Webster Unit, Solomon Division, Pick</t>
+          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
@@ -16084,17 +16184,17 @@
       </c>
       <c r="G131" s="20" t="inlineStr">
         <is>
-          <t>$7.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H131" s="20" t="inlineStr">
         <is>
-          <t>Aug 10, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I131" s="20" t="inlineStr">
         <is>
-          <t>48d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J131" s="20" t="inlineStr">
@@ -16111,57 +16211,109 @@
     <row r="132" ht="28" customHeight="1">
       <c r="B132" s="17" t="inlineStr">
         <is>
+          <t>140R6026R0016</t>
+        </is>
+      </c>
+      <c r="C132" s="30" t="inlineStr">
+        <is>
+          <t>Z--Webster Dam, Spillway Radial Gates Repair, Webster Unit, Solomon Division, Pick</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G132" s="17" t="inlineStr">
+        <is>
+          <t>$7.5M</t>
+        </is>
+      </c>
+      <c r="H132" s="17" t="inlineStr">
+        <is>
+          <t>Aug 10, 2026</t>
+        </is>
+      </c>
+      <c r="I132" s="17" t="inlineStr">
+        <is>
+          <t>48d</t>
+        </is>
+      </c>
+      <c r="J132" s="17" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K132" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="B133" s="20" t="inlineStr">
+        <is>
           <t>W9127826RA025</t>
         </is>
       </c>
-      <c r="C132" s="30" t="inlineStr">
+      <c r="C133" s="33" t="inlineStr">
         <is>
           <t>Phillips Parkway Haul Route</t>
         </is>
       </c>
-      <c r="D132" s="17" t="inlineStr">
+      <c r="D133" s="20" t="inlineStr">
         <is>
           <t>Cape Canaveral, Florida</t>
         </is>
       </c>
-      <c r="E132" s="17" t="inlineStr">
+      <c r="E133" s="20" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F132" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G132" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H132" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I132" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J132" s="17" t="inlineStr">
+      <c r="F133" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G133" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H133" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I133" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J133" s="20" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="K132" s="32" t="inlineStr">
+      <c r="K133" s="35" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K132"/>
+  <autoFilter ref="B5:K133"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -16294,6 +16446,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16306,7 +16459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K72"/>
+  <dimension ref="B2:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -16334,7 +16487,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="45" t="inlineStr">
         <is>
-          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  67 records  (9 SDVOSB)  ·  June 22, 2026</t>
+          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  68 records  (9 SDVOSB)  ·  June 22, 2026</t>
         </is>
       </c>
     </row>
@@ -18739,12 +18892,12 @@
       </c>
       <c r="C51" s="53" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>LARO-DRILL NEW WATER WELL - SHERMAN HOMES CABINS</t>
         </is>
       </c>
       <c r="D51" s="54" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E51" s="54" t="inlineStr">
@@ -18754,17 +18907,17 @@
       </c>
       <c r="F51" s="54" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="54" t="inlineStr">
         <is>
-          <t>Jul 20, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="H51" s="54" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>24d</t>
         </is>
       </c>
       <c r="I51" s="54" t="inlineStr">
@@ -18791,12 +18944,12 @@
       </c>
       <c r="C52" s="30" t="inlineStr">
         <is>
-          <t>Z--KNRI REPLACE VC SANITARY PLUMBING/SEPTIC</t>
+          <t>Rosebud Lift Station Construction</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t>Stanton, North Dakota</t>
+          <t>Rosebud, South Dakota</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
@@ -18806,17 +18959,17 @@
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.8M</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Jul 20, 2026</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
@@ -18824,9 +18977,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J52" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J52" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K52" s="32" t="inlineStr">
@@ -18838,17 +18991,17 @@
     <row r="53" ht="28" customHeight="1">
       <c r="B53" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C53" s="53" t="inlineStr">
         <is>
-          <t>Z--Rehab Power and Cooling Systems, Pinnalces NP</t>
+          <t>Z--KNRI REPLACE VC SANITARY PLUMBING/SEPTIC</t>
         </is>
       </c>
       <c r="D53" s="54" t="inlineStr">
         <is>
-          <t>Paicines</t>
+          <t>Stanton, North Dakota</t>
         </is>
       </c>
       <c r="E53" s="54" t="inlineStr">
@@ -18895,12 +19048,12 @@
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>23 STS HPTC Surround Sound Installation</t>
+          <t>Z--Rehab Power and Cooling Systems, Pinnalces NP</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>Hurlburt Field, Florida</t>
+          <t>Paicines</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
@@ -18942,17 +19095,17 @@
     <row r="55" ht="28" customHeight="1">
       <c r="B55" s="52" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C55" s="53" t="inlineStr">
         <is>
-          <t>VA-RAPPAHANNOCK RIV NWR-WELL DRILLING</t>
+          <t>23 STS HPTC Surround Sound Installation</t>
         </is>
       </c>
       <c r="D55" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Hurlburt Field, Florida</t>
         </is>
       </c>
       <c r="E55" s="54" t="inlineStr">
@@ -18994,12 +19147,12 @@
     <row r="56" ht="28" customHeight="1">
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
+          <t>VA-RAPPAHANNOCK RIV NWR-WELL DRILLING</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -19051,7 +19204,7 @@
       </c>
       <c r="C57" s="53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AIRR Security Cameras &amp; Badging for BTFA</t>
+          <t>61--AR-MAMMOTH SPRING NFH-REPLACE GENERATOR</t>
         </is>
       </c>
       <c r="D57" s="54" t="inlineStr">
@@ -19098,12 +19251,12 @@
     <row r="58" ht="28" customHeight="1">
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
+          <t xml:space="preserve"> AIRR Security Cameras &amp; Badging for BTFA</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
@@ -19150,12 +19303,12 @@
     <row r="59" ht="28" customHeight="1">
       <c r="B59" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C59" s="53" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>NM - SW NATIVE ARC - 5-Year BPA for Well Repair</t>
         </is>
       </c>
       <c r="D59" s="54" t="inlineStr">
@@ -19175,17 +19328,17 @@
       </c>
       <c r="G59" s="54" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="H59" s="54" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I59" s="54" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="J59" s="18" t="inlineStr">
@@ -19202,17 +19355,17 @@
     <row r="60" ht="28" customHeight="1">
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
@@ -19227,12 +19380,12 @@
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
@@ -19254,17 +19407,17 @@
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="52" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C61" s="53" t="inlineStr">
         <is>
-          <t>Air National Guard (ANG) Smart Meters</t>
+          <t>Feeder #7 Repair</t>
         </is>
       </c>
       <c r="D61" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Selfridge ANGB, Michigan</t>
         </is>
       </c>
       <c r="E61" s="54" t="inlineStr">
@@ -19274,17 +19427,17 @@
       </c>
       <c r="F61" s="54" t="inlineStr">
         <is>
-          <t>$4.2M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G61" s="54" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="H61" s="54" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="I61" s="54" t="inlineStr">
@@ -19306,17 +19459,17 @@
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>Air National Guard (ANG) Smart Meters</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
@@ -19326,17 +19479,17 @@
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$4.2M</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
@@ -19344,9 +19497,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J62" s="41" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
+      <c r="J62" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K62" s="32" t="inlineStr">
@@ -19358,17 +19511,17 @@
     <row r="63" ht="28" customHeight="1">
       <c r="B63" s="52" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C63" s="53" t="inlineStr">
         <is>
-          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D63" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E63" s="54" t="inlineStr">
@@ -19383,12 +19536,12 @@
       </c>
       <c r="G63" s="54" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H63" s="54" t="inlineStr">
         <is>
-          <t>23d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="I63" s="54" t="inlineStr">
@@ -19415,7 +19568,7 @@
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -19435,12 +19588,12 @@
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>31d</t>
+          <t>23d</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
@@ -19448,9 +19601,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J64" s="42" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J64" s="41" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K64" s="32" t="inlineStr">
@@ -19467,7 +19620,7 @@
       </c>
       <c r="C65" s="53" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D65" s="54" t="inlineStr">
@@ -19514,17 +19667,17 @@
     <row r="66" ht="28" customHeight="1">
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C66" s="30" t="inlineStr">
         <is>
-          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>Pine Ridge, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -19534,17 +19687,17 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>Jul 31, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>38d</t>
+          <t>31d</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
@@ -19571,12 +19724,12 @@
       </c>
       <c r="C67" s="53" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
         </is>
       </c>
       <c r="D67" s="54" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Pine Ridge, South Dakota</t>
         </is>
       </c>
       <c r="E67" s="54" t="inlineStr">
@@ -19586,17 +19739,17 @@
       </c>
       <c r="F67" s="54" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="G67" s="54" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 31, 2026</t>
         </is>
       </c>
       <c r="H67" s="54" t="inlineStr">
         <is>
-          <t>66d</t>
+          <t>38d</t>
         </is>
       </c>
       <c r="I67" s="54" t="inlineStr">
@@ -19623,7 +19776,7 @@
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -19638,17 +19791,17 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>$5.1M</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>Jun 23, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>66d</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
@@ -19656,9 +19809,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J68" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J68" s="42" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K68" s="32" t="inlineStr">
@@ -19670,12 +19823,12 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="52" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C69" s="53" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D69" s="54" t="inlineStr">
@@ -19690,17 +19843,17 @@
       </c>
       <c r="F69" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$5.1M</t>
         </is>
       </c>
       <c r="G69" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 23, 2026</t>
         </is>
       </c>
       <c r="H69" s="54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I69" s="54" t="inlineStr">
@@ -19708,9 +19861,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J69" s="42" t="inlineStr">
-        <is>
-          <t>Pre-Sol</t>
+      <c r="J69" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K69" s="55" t="inlineStr">
@@ -19727,12 +19880,12 @@
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>Stockton, Missouri</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -19774,17 +19927,17 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="52" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C71" s="53" t="inlineStr">
         <is>
-          <t>USACE SPK DB Construction – DDJC Centralized Gas and Electric Metering - Tracy, CA</t>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
         </is>
       </c>
       <c r="D71" s="54" t="inlineStr">
         <is>
-          <t>Tracy, California</t>
+          <t>Stockton, Missouri</t>
         </is>
       </c>
       <c r="E71" s="54" t="inlineStr">
@@ -19794,7 +19947,7 @@
       </c>
       <c r="F71" s="54" t="inlineStr">
         <is>
-          <t>$7.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G71" s="54" t="inlineStr">
@@ -19826,57 +19979,109 @@
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="16" t="inlineStr">
         <is>
+          <t>237130 — Power &amp; Communication Line</t>
+        </is>
+      </c>
+      <c r="C72" s="30" t="inlineStr">
+        <is>
+          <t>USACE SPK DB Construction – DDJC Centralized Gas and Electric Metering - Tracy, CA</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>Tracy, California</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>$7.5M</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J72" s="42" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="B73" s="52" t="inlineStr">
+        <is>
           <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
-      <c r="C72" s="30" t="inlineStr">
+      <c r="C73" s="53" t="inlineStr">
         <is>
           <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E72" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="F72" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="17" t="inlineStr">
+      <c r="D73" s="54" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E73" s="54" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F73" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="54" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="H72" s="17" t="inlineStr">
+      <c r="H73" s="54" t="inlineStr">
         <is>
           <t>7d</t>
         </is>
       </c>
-      <c r="I72" s="17" t="inlineStr">
+      <c r="I73" s="54" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="J72" s="18" t="inlineStr">
+      <c r="J73" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="K72" s="32" t="inlineStr">
+      <c r="K73" s="55" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K72"/>
+  <autoFilter ref="B5:K73"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -19949,6 +20154,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
